--- a/downloads/indicadores/IGAE/IGAE_datos.xlsx
+++ b/downloads/indicadores/IGAE/IGAE_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O407"/>
+  <dimension ref="A1:O408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22602,31 +22602,31 @@
         <v>46174</v>
       </c>
       <c r="C407" s="9" t="n">
-        <v>107.449582</v>
+        <v>107.390831</v>
       </c>
       <c r="D407" s="10" t="n">
         <v>-0.001</v>
       </c>
       <c r="E407" s="10" t="n">
-        <v>0.028191</v>
+        <v>0.027629</v>
       </c>
       <c r="F407" s="9" t="n">
-        <v>111.293453</v>
+        <v>111.311207</v>
       </c>
       <c r="G407" s="10" t="n">
-        <v>0.00496</v>
+        <v>0.00512</v>
       </c>
       <c r="H407" s="9" t="n">
-        <v>102.597063</v>
+        <v>102.52517</v>
       </c>
       <c r="I407" s="10" t="n">
-        <v>0.017117</v>
+        <v>0.016405</v>
       </c>
       <c r="J407" s="9" t="n">
-        <v>109.991856</v>
+        <v>109.93631</v>
       </c>
       <c r="K407" s="10" t="n">
-        <v>0.035514</v>
+        <v>0.034991</v>
       </c>
       <c r="L407" s="11" t="inlineStr">
         <is>
@@ -22644,6 +22644,61 @@
         </is>
       </c>
       <c r="O407" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="4" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B408" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C408" s="6" t="n">
+        <v>109.210136</v>
+      </c>
+      <c r="D408" s="7" t="n"/>
+      <c r="E408" s="7" t="n">
+        <v>0.033585</v>
+      </c>
+      <c r="F408" s="6" t="n">
+        <v>101.391452</v>
+      </c>
+      <c r="G408" s="7" t="n">
+        <v>-0.010622</v>
+      </c>
+      <c r="H408" s="6" t="n">
+        <v>104.283536</v>
+      </c>
+      <c r="I408" s="7" t="n">
+        <v>0.026621</v>
+      </c>
+      <c r="J408" s="6" t="n">
+        <v>112.444236</v>
+      </c>
+      <c r="K408" s="7" t="n">
+        <v>0.039634</v>
+      </c>
+      <c r="L408" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="M408" s="8" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="N408" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="O408" s="8" t="inlineStr">
         <is>
           <t>24 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/IGAE/IGAE_datos.xlsx
+++ b/downloads/indicadores/IGAE/IGAE_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O408"/>
+  <dimension ref="A1:O409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22659,29 +22659,29 @@
         <v>46204</v>
       </c>
       <c r="C408" s="6" t="n">
-        <v>109.210136</v>
+        <v>109.262414</v>
       </c>
       <c r="D408" s="7" t="n"/>
       <c r="E408" s="7" t="n">
-        <v>0.033585</v>
+        <v>0.03408</v>
       </c>
       <c r="F408" s="6" t="n">
-        <v>101.391452</v>
+        <v>101.413482</v>
       </c>
       <c r="G408" s="7" t="n">
-        <v>-0.010622</v>
+        <v>-0.010407</v>
       </c>
       <c r="H408" s="6" t="n">
-        <v>104.283536</v>
+        <v>104.283391</v>
       </c>
       <c r="I408" s="7" t="n">
-        <v>0.026621</v>
+        <v>0.02662</v>
       </c>
       <c r="J408" s="6" t="n">
-        <v>112.444236</v>
+        <v>112.527977</v>
       </c>
       <c r="K408" s="7" t="n">
-        <v>0.039634</v>
+        <v>0.040408</v>
       </c>
       <c r="L408" s="8" t="inlineStr">
         <is>
@@ -22699,6 +22699,61 @@
         </is>
       </c>
       <c r="O408" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B409" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C409" s="9" t="n">
+        <v>108.317094</v>
+      </c>
+      <c r="D409" s="10" t="n"/>
+      <c r="E409" s="10" t="n">
+        <v>0.033335</v>
+      </c>
+      <c r="F409" s="9" t="n">
+        <v>97.14478699999999</v>
+      </c>
+      <c r="G409" s="10" t="n">
+        <v>-0.025795</v>
+      </c>
+      <c r="H409" s="9" t="n">
+        <v>104.933926</v>
+      </c>
+      <c r="I409" s="10" t="n">
+        <v>0.034974</v>
+      </c>
+      <c r="J409" s="9" t="n">
+        <v>110.861301</v>
+      </c>
+      <c r="K409" s="10" t="n">
+        <v>0.035521</v>
+      </c>
+      <c r="L409" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="M409" s="11" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="N409" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="O409" s="11" t="inlineStr">
         <is>
           <t>24 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/IGAE/IGAE_datos.xlsx
+++ b/downloads/indicadores/IGAE/IGAE_datos.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf · Fecha de publicación: 24 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf · Fecha de publicación: 23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O12" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O14" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O16" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O18" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O22" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O28" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O32" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2030,12 +2030,12 @@
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O36" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O38" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2415,12 +2415,12 @@
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O40" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O42" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2580,12 @@
       </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O44" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2690,12 +2690,12 @@
       </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2800,12 +2800,12 @@
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2855,12 +2855,12 @@
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O48" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O50" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3075,12 +3075,12 @@
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O52" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3185,12 @@
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O54" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O56" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O58" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3625,12 @@
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3735,12 +3735,12 @@
       </c>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O64" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O65" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3845,12 +3845,12 @@
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O66" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O67" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3955,12 +3955,12 @@
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O68" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O69" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4065,12 +4065,12 @@
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O70" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4120,12 @@
       </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4175,12 @@
       </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O72" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4285,12 @@
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O74" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4340,12 +4340,12 @@
       </c>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O75" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O76" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O78" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O80" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4670,12 @@
       </c>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O81" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O82" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4780,12 +4780,12 @@
       </c>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O83" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4835,12 +4835,12 @@
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O84" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O85" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O86" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5000,12 +5000,12 @@
       </c>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O87" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="N88" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O88" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5110,12 +5110,12 @@
       </c>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O89" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="N90" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O90" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5220,12 +5220,12 @@
       </c>
       <c r="N91" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O91" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="N92" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O92" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="N93" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O93" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="N94" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O94" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="N95" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O95" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="N96" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O96" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5550,12 +5550,12 @@
       </c>
       <c r="N97" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O97" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="N98" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O98" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5660,12 +5660,12 @@
       </c>
       <c r="N99" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O99" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5715,12 +5715,12 @@
       </c>
       <c r="N100" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O100" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="N101" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O101" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5825,12 +5825,12 @@
       </c>
       <c r="N102" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O102" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5880,12 +5880,12 @@
       </c>
       <c r="N103" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O103" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5935,12 +5935,12 @@
       </c>
       <c r="N104" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O104" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5990,12 +5990,12 @@
       </c>
       <c r="N105" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O105" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6045,12 +6045,12 @@
       </c>
       <c r="N106" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O106" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="N107" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O107" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6155,12 +6155,12 @@
       </c>
       <c r="N108" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O108" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="N109" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O109" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6265,12 +6265,12 @@
       </c>
       <c r="N110" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O110" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6320,12 +6320,12 @@
       </c>
       <c r="N111" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O111" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="N112" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O112" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6430,12 +6430,12 @@
       </c>
       <c r="N113" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O113" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6485,12 +6485,12 @@
       </c>
       <c r="N114" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O114" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6540,12 +6540,12 @@
       </c>
       <c r="N115" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O115" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="N116" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O116" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="N117" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O117" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="N118" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O118" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="N119" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O119" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="N120" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O120" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="N121" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O121" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="N122" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O122" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="N123" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O123" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7035,12 +7035,12 @@
       </c>
       <c r="N124" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O124" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="N125" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O125" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="N126" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O126" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="N127" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7255,12 +7255,12 @@
       </c>
       <c r="N128" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O128" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7310,12 +7310,12 @@
       </c>
       <c r="N129" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7365,12 +7365,12 @@
       </c>
       <c r="N130" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O130" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7420,12 +7420,12 @@
       </c>
       <c r="N131" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O131" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7475,12 +7475,12 @@
       </c>
       <c r="N132" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O132" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="N133" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O133" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="N134" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O134" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7640,12 +7640,12 @@
       </c>
       <c r="N135" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7695,12 +7695,12 @@
       </c>
       <c r="N136" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O136" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7750,12 +7750,12 @@
       </c>
       <c r="N137" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O137" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7805,12 +7805,12 @@
       </c>
       <c r="N138" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O138" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="N139" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O139" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7915,12 +7915,12 @@
       </c>
       <c r="N140" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O140" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7970,12 +7970,12 @@
       </c>
       <c r="N141" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O141" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="N142" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O142" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8080,12 +8080,12 @@
       </c>
       <c r="N143" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O143" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="N144" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O144" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8190,12 +8190,12 @@
       </c>
       <c r="N145" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8245,12 +8245,12 @@
       </c>
       <c r="N146" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O146" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8300,12 +8300,12 @@
       </c>
       <c r="N147" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="N148" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O148" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8410,12 +8410,12 @@
       </c>
       <c r="N149" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8465,12 +8465,12 @@
       </c>
       <c r="N150" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O150" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="N151" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="N152" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O152" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8630,12 @@
       </c>
       <c r="N153" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O153" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="N154" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O154" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8740,12 +8740,12 @@
       </c>
       <c r="N155" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O155" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8795,12 +8795,12 @@
       </c>
       <c r="N156" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O156" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="N157" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="N158" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O158" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8960,12 +8960,12 @@
       </c>
       <c r="N159" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9015,12 +9015,12 @@
       </c>
       <c r="N160" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O160" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9070,12 +9070,12 @@
       </c>
       <c r="N161" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9125,12 +9125,12 @@
       </c>
       <c r="N162" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O162" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="N163" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9235,12 +9235,12 @@
       </c>
       <c r="N164" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O164" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9290,12 +9290,12 @@
       </c>
       <c r="N165" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="N166" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O166" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9400,12 +9400,12 @@
       </c>
       <c r="N167" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O167" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9455,12 +9455,12 @@
       </c>
       <c r="N168" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O168" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9510,12 +9510,12 @@
       </c>
       <c r="N169" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O169" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9565,12 +9565,12 @@
       </c>
       <c r="N170" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O170" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9620,12 +9620,12 @@
       </c>
       <c r="N171" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="N172" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O172" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9730,12 +9730,12 @@
       </c>
       <c r="N173" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9785,12 +9785,12 @@
       </c>
       <c r="N174" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O174" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9840,12 +9840,12 @@
       </c>
       <c r="N175" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9895,12 +9895,12 @@
       </c>
       <c r="N176" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O176" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="N177" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="N178" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O178" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="N179" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O179" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10115,12 +10115,12 @@
       </c>
       <c r="N180" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O180" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="N181" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O181" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="N182" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O182" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="N183" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O183" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="N184" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O184" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10390,12 +10390,12 @@
       </c>
       <c r="N185" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O185" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10445,12 +10445,12 @@
       </c>
       <c r="N186" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O186" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10500,12 +10500,12 @@
       </c>
       <c r="N187" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O187" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10555,12 +10555,12 @@
       </c>
       <c r="N188" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O188" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10610,12 +10610,12 @@
       </c>
       <c r="N189" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O189" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10665,12 +10665,12 @@
       </c>
       <c r="N190" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O190" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10720,12 +10720,12 @@
       </c>
       <c r="N191" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O191" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10775,12 +10775,12 @@
       </c>
       <c r="N192" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O192" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10830,12 +10830,12 @@
       </c>
       <c r="N193" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O193" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10885,12 +10885,12 @@
       </c>
       <c r="N194" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O194" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10940,12 +10940,12 @@
       </c>
       <c r="N195" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O195" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10995,12 +10995,12 @@
       </c>
       <c r="N196" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O196" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11050,12 +11050,12 @@
       </c>
       <c r="N197" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O197" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="N198" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O198" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11160,12 +11160,12 @@
       </c>
       <c r="N199" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O199" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="N200" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O200" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11270,12 +11270,12 @@
       </c>
       <c r="N201" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O201" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11325,12 +11325,12 @@
       </c>
       <c r="N202" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O202" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11380,12 @@
       </c>
       <c r="N203" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O203" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11435,12 +11435,12 @@
       </c>
       <c r="N204" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O204" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11490,12 +11490,12 @@
       </c>
       <c r="N205" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O205" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11545,12 +11545,12 @@
       </c>
       <c r="N206" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O206" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11600,12 +11600,12 @@
       </c>
       <c r="N207" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O207" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11655,12 +11655,12 @@
       </c>
       <c r="N208" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O208" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11710,12 +11710,12 @@
       </c>
       <c r="N209" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O209" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11765,12 +11765,12 @@
       </c>
       <c r="N210" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O210" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11820,12 +11820,12 @@
       </c>
       <c r="N211" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O211" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11875,12 +11875,12 @@
       </c>
       <c r="N212" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O212" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11930,12 +11930,12 @@
       </c>
       <c r="N213" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O213" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11985,12 +11985,12 @@
       </c>
       <c r="N214" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O214" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12040,12 +12040,12 @@
       </c>
       <c r="N215" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O215" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12095,12 +12095,12 @@
       </c>
       <c r="N216" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O216" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12150,12 +12150,12 @@
       </c>
       <c r="N217" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O217" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12205,12 +12205,12 @@
       </c>
       <c r="N218" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O218" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12260,12 +12260,12 @@
       </c>
       <c r="N219" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O219" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12315,12 +12315,12 @@
       </c>
       <c r="N220" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O220" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12370,12 +12370,12 @@
       </c>
       <c r="N221" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O221" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="N222" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O222" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12480,12 +12480,12 @@
       </c>
       <c r="N223" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O223" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12535,12 +12535,12 @@
       </c>
       <c r="N224" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O224" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12590,12 +12590,12 @@
       </c>
       <c r="N225" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O225" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12645,12 +12645,12 @@
       </c>
       <c r="N226" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O226" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12700,12 +12700,12 @@
       </c>
       <c r="N227" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O227" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12755,12 +12755,12 @@
       </c>
       <c r="N228" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O228" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="N229" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O229" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12865,12 +12865,12 @@
       </c>
       <c r="N230" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O230" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="N231" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O231" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12975,12 +12975,12 @@
       </c>
       <c r="N232" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O232" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13030,12 +13030,12 @@
       </c>
       <c r="N233" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O233" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13085,12 +13085,12 @@
       </c>
       <c r="N234" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O234" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13140,12 +13140,12 @@
       </c>
       <c r="N235" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O235" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13195,12 +13195,12 @@
       </c>
       <c r="N236" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O236" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13250,12 +13250,12 @@
       </c>
       <c r="N237" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O237" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13305,12 +13305,12 @@
       </c>
       <c r="N238" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O238" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13360,12 +13360,12 @@
       </c>
       <c r="N239" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O239" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13415,12 +13415,12 @@
       </c>
       <c r="N240" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O240" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13470,12 +13470,12 @@
       </c>
       <c r="N241" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O241" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13525,12 +13525,12 @@
       </c>
       <c r="N242" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O242" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13580,12 +13580,12 @@
       </c>
       <c r="N243" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O243" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13635,12 +13635,12 @@
       </c>
       <c r="N244" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O244" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="N245" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O245" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="N246" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O246" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13800,12 +13800,12 @@
       </c>
       <c r="N247" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O247" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13855,12 +13855,12 @@
       </c>
       <c r="N248" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O248" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13910,12 +13910,12 @@
       </c>
       <c r="N249" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O249" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13965,12 +13965,12 @@
       </c>
       <c r="N250" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O250" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14020,12 +14020,12 @@
       </c>
       <c r="N251" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O251" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14075,12 +14075,12 @@
       </c>
       <c r="N252" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O252" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14130,12 +14130,12 @@
       </c>
       <c r="N253" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O253" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14185,12 +14185,12 @@
       </c>
       <c r="N254" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O254" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14240,12 +14240,12 @@
       </c>
       <c r="N255" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O255" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="N256" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O256" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14350,12 +14350,12 @@
       </c>
       <c r="N257" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O257" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14405,12 +14405,12 @@
       </c>
       <c r="N258" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O258" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14460,12 +14460,12 @@
       </c>
       <c r="N259" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O259" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14515,12 +14515,12 @@
       </c>
       <c r="N260" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O260" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14570,12 +14570,12 @@
       </c>
       <c r="N261" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O261" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14625,12 +14625,12 @@
       </c>
       <c r="N262" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O262" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14680,12 +14680,12 @@
       </c>
       <c r="N263" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O263" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14735,12 +14735,12 @@
       </c>
       <c r="N264" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O264" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14790,12 +14790,12 @@
       </c>
       <c r="N265" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O265" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14845,12 +14845,12 @@
       </c>
       <c r="N266" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O266" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14900,12 +14900,12 @@
       </c>
       <c r="N267" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O267" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14955,12 +14955,12 @@
       </c>
       <c r="N268" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O268" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15010,12 +15010,12 @@
       </c>
       <c r="N269" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O269" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15065,12 +15065,12 @@
       </c>
       <c r="N270" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O270" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15120,12 +15120,12 @@
       </c>
       <c r="N271" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O271" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15175,12 +15175,12 @@
       </c>
       <c r="N272" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O272" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15230,12 +15230,12 @@
       </c>
       <c r="N273" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O273" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15285,12 +15285,12 @@
       </c>
       <c r="N274" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O274" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15340,12 +15340,12 @@
       </c>
       <c r="N275" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O275" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15395,12 +15395,12 @@
       </c>
       <c r="N276" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O276" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15450,12 +15450,12 @@
       </c>
       <c r="N277" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O277" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15505,12 +15505,12 @@
       </c>
       <c r="N278" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O278" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15560,12 +15560,12 @@
       </c>
       <c r="N279" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O279" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="N280" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O280" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15670,12 +15670,12 @@
       </c>
       <c r="N281" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O281" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15725,12 +15725,12 @@
       </c>
       <c r="N282" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O282" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15780,12 +15780,12 @@
       </c>
       <c r="N283" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O283" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15835,12 +15835,12 @@
       </c>
       <c r="N284" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O284" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15890,12 +15890,12 @@
       </c>
       <c r="N285" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O285" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15945,12 +15945,12 @@
       </c>
       <c r="N286" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O286" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16000,12 +16000,12 @@
       </c>
       <c r="N287" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O287" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16055,12 +16055,12 @@
       </c>
       <c r="N288" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O288" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16110,12 +16110,12 @@
       </c>
       <c r="N289" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O289" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16165,12 +16165,12 @@
       </c>
       <c r="N290" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O290" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16220,12 +16220,12 @@
       </c>
       <c r="N291" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O291" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="N292" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O292" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16330,12 +16330,12 @@
       </c>
       <c r="N293" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O293" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16385,12 +16385,12 @@
       </c>
       <c r="N294" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O294" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16440,12 +16440,12 @@
       </c>
       <c r="N295" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O295" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16495,12 +16495,12 @@
       </c>
       <c r="N296" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O296" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16550,12 +16550,12 @@
       </c>
       <c r="N297" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O297" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16605,12 +16605,12 @@
       </c>
       <c r="N298" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O298" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16660,12 +16660,12 @@
       </c>
       <c r="N299" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O299" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="N300" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O300" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16770,12 +16770,12 @@
       </c>
       <c r="N301" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O301" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16825,12 +16825,12 @@
       </c>
       <c r="N302" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O302" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16880,12 +16880,12 @@
       </c>
       <c r="N303" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O303" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16935,12 +16935,12 @@
       </c>
       <c r="N304" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O304" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16990,12 +16990,12 @@
       </c>
       <c r="N305" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O305" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17045,12 +17045,12 @@
       </c>
       <c r="N306" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O306" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17100,12 +17100,12 @@
       </c>
       <c r="N307" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O307" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17155,12 +17155,12 @@
       </c>
       <c r="N308" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O308" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17210,12 +17210,12 @@
       </c>
       <c r="N309" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O309" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17265,12 +17265,12 @@
       </c>
       <c r="N310" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O310" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17320,12 +17320,12 @@
       </c>
       <c r="N311" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O311" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17375,12 +17375,12 @@
       </c>
       <c r="N312" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O312" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17430,12 +17430,12 @@
       </c>
       <c r="N313" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O313" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17485,12 +17485,12 @@
       </c>
       <c r="N314" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O314" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="N315" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O315" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17595,12 +17595,12 @@
       </c>
       <c r="N316" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O316" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17650,12 +17650,12 @@
       </c>
       <c r="N317" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O317" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="N318" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O318" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17760,12 +17760,12 @@
       </c>
       <c r="N319" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O319" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17815,12 +17815,12 @@
       </c>
       <c r="N320" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O320" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17870,12 +17870,12 @@
       </c>
       <c r="N321" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O321" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17925,12 +17925,12 @@
       </c>
       <c r="N322" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O322" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -17980,12 +17980,12 @@
       </c>
       <c r="N323" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O323" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18035,12 +18035,12 @@
       </c>
       <c r="N324" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O324" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18090,12 +18090,12 @@
       </c>
       <c r="N325" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O325" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18145,12 +18145,12 @@
       </c>
       <c r="N326" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O326" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18200,12 +18200,12 @@
       </c>
       <c r="N327" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O327" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18255,12 +18255,12 @@
       </c>
       <c r="N328" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O328" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18310,12 +18310,12 @@
       </c>
       <c r="N329" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O329" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18365,12 +18365,12 @@
       </c>
       <c r="N330" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O330" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18420,12 +18420,12 @@
       </c>
       <c r="N331" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O331" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18475,12 +18475,12 @@
       </c>
       <c r="N332" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O332" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18530,12 +18530,12 @@
       </c>
       <c r="N333" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O333" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18585,12 +18585,12 @@
       </c>
       <c r="N334" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O334" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18640,12 +18640,12 @@
       </c>
       <c r="N335" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O335" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18695,12 +18695,12 @@
       </c>
       <c r="N336" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O336" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18750,12 +18750,12 @@
       </c>
       <c r="N337" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O337" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18805,12 +18805,12 @@
       </c>
       <c r="N338" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O338" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18860,12 +18860,12 @@
       </c>
       <c r="N339" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O339" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18915,12 +18915,12 @@
       </c>
       <c r="N340" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O340" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -18970,12 +18970,12 @@
       </c>
       <c r="N341" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O341" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19025,12 +19025,12 @@
       </c>
       <c r="N342" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O342" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19080,12 +19080,12 @@
       </c>
       <c r="N343" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O343" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19135,12 +19135,12 @@
       </c>
       <c r="N344" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O344" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19190,12 +19190,12 @@
       </c>
       <c r="N345" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O345" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19245,12 +19245,12 @@
       </c>
       <c r="N346" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O346" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19300,12 +19300,12 @@
       </c>
       <c r="N347" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O347" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19355,12 +19355,12 @@
       </c>
       <c r="N348" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O348" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19410,12 +19410,12 @@
       </c>
       <c r="N349" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O349" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19465,12 +19465,12 @@
       </c>
       <c r="N350" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O350" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19520,12 +19520,12 @@
       </c>
       <c r="N351" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O351" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19575,12 +19575,12 @@
       </c>
       <c r="N352" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O352" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19630,12 +19630,12 @@
       </c>
       <c r="N353" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O353" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19685,12 +19685,12 @@
       </c>
       <c r="N354" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O354" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19740,12 +19740,12 @@
       </c>
       <c r="N355" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O355" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19795,12 +19795,12 @@
       </c>
       <c r="N356" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O356" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19850,12 +19850,12 @@
       </c>
       <c r="N357" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O357" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19905,12 +19905,12 @@
       </c>
       <c r="N358" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O358" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -19960,12 +19960,12 @@
       </c>
       <c r="N359" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O359" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20015,12 +20015,12 @@
       </c>
       <c r="N360" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O360" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20070,12 +20070,12 @@
       </c>
       <c r="N361" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O361" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20125,12 +20125,12 @@
       </c>
       <c r="N362" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O362" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20180,12 +20180,12 @@
       </c>
       <c r="N363" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O363" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20235,12 +20235,12 @@
       </c>
       <c r="N364" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O364" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20290,12 +20290,12 @@
       </c>
       <c r="N365" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O365" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20345,12 +20345,12 @@
       </c>
       <c r="N366" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O366" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20400,12 +20400,12 @@
       </c>
       <c r="N367" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O367" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20455,12 +20455,12 @@
       </c>
       <c r="N368" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O368" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20510,12 +20510,12 @@
       </c>
       <c r="N369" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O369" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20565,12 +20565,12 @@
       </c>
       <c r="N370" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O370" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20620,12 +20620,12 @@
       </c>
       <c r="N371" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O371" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20675,12 +20675,12 @@
       </c>
       <c r="N372" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O372" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20730,12 +20730,12 @@
       </c>
       <c r="N373" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O373" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20785,12 +20785,12 @@
       </c>
       <c r="N374" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O374" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20840,12 +20840,12 @@
       </c>
       <c r="N375" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O375" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20895,12 +20895,12 @@
       </c>
       <c r="N376" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O376" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20950,12 +20950,12 @@
       </c>
       <c r="N377" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O377" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21005,12 +21005,12 @@
       </c>
       <c r="N378" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O378" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21060,12 +21060,12 @@
       </c>
       <c r="N379" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O379" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21115,12 +21115,12 @@
       </c>
       <c r="N380" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O380" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21170,12 +21170,12 @@
       </c>
       <c r="N381" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O381" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21225,12 +21225,12 @@
       </c>
       <c r="N382" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O382" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21280,12 +21280,12 @@
       </c>
       <c r="N383" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O383" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="N384" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O384" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21390,12 +21390,12 @@
       </c>
       <c r="N385" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O385" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21445,12 +21445,12 @@
       </c>
       <c r="N386" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O386" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21500,12 +21500,12 @@
       </c>
       <c r="N387" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O387" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21557,12 +21557,12 @@
       </c>
       <c r="N388" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O388" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21614,12 +21614,12 @@
       </c>
       <c r="N389" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O389" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21671,12 +21671,12 @@
       </c>
       <c r="N390" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O390" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21728,12 +21728,12 @@
       </c>
       <c r="N391" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O391" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21785,12 +21785,12 @@
       </c>
       <c r="N392" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O392" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="N393" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O393" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21899,12 +21899,12 @@
       </c>
       <c r="N394" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O394" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="N395" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O395" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22013,12 +22013,12 @@
       </c>
       <c r="N396" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O396" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22070,12 +22070,12 @@
       </c>
       <c r="N397" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O397" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22127,12 +22127,12 @@
       </c>
       <c r="N398" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O398" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22184,12 +22184,12 @@
       </c>
       <c r="N399" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O399" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="N400" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O400" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22298,12 +22298,12 @@
       </c>
       <c r="N401" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O401" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22355,12 +22355,12 @@
       </c>
       <c r="N402" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O402" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22412,12 +22412,12 @@
       </c>
       <c r="N403" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O403" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22469,12 +22469,12 @@
       </c>
       <c r="N404" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O404" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22526,12 +22526,12 @@
       </c>
       <c r="N405" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O405" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22583,12 +22583,12 @@
       </c>
       <c r="N406" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O406" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22640,12 +22640,12 @@
       </c>
       <c r="N407" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O407" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22661,7 +22661,9 @@
       <c r="C408" s="6" t="n">
         <v>109.262414</v>
       </c>
-      <c r="D408" s="7" t="n"/>
+      <c r="D408" s="7" t="n">
+        <v>0.008</v>
+      </c>
       <c r="E408" s="7" t="n">
         <v>0.03408</v>
       </c>
@@ -22695,12 +22697,12 @@
       </c>
       <c r="N408" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O408" s="8" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -22716,7 +22718,9 @@
       <c r="C409" s="9" t="n">
         <v>108.317094</v>
       </c>
-      <c r="D409" s="10" t="n"/>
+      <c r="D409" s="10" t="n">
+        <v>0.006</v>
+      </c>
       <c r="E409" s="10" t="n">
         <v>0.033335</v>
       </c>
@@ -22750,12 +22754,12 @@
       </c>
       <c r="N409" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_10.pdf</t>
         </is>
       </c>
       <c r="O409" s="11" t="inlineStr">
         <is>
-          <t>24 de agosto de 2026</t>
+          <t>23 de octubre de 2026</t>
         </is>
       </c>
     </row>
